--- a/Assets/Docs/SunWave/Sunlight_SS_12_10_25_APS_LEDs_+_Lipod_Silver_+_LIGER_22_Satin.xlsx
+++ b/Assets/Docs/SunWave/Sunlight_SS_12_10_25_APS_LEDs_+_Lipod_Silver_+_LIGER_22_Satin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Projects\Spectrum\Assets\Docs\SunWave\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4451580E-F1E1-437B-A818-0E66793243D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2D5540-D108-4B05-B186-BC69380D0FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="6630" windowWidth="29040" windowHeight="16440" xr2:uid="{F052045B-BEDD-47AA-85F9-96DF3A1BCB60}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -165,7 +163,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +178,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -229,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -250,6 +258,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -586,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8456A2ED-A584-48DA-B74C-C107E475F514}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="13.7109375" customWidth="1"/>
@@ -607,7 +625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -624,7 +642,7 @@
         <v>0.46200000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -641,7 +659,7 @@
         <v>0.47199999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -658,7 +676,7 @@
         <v>0.47199999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -675,7 +693,7 @@
         <v>0.50800000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -692,7 +710,7 @@
         <v>0.55700000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -709,7 +727,7 @@
         <v>0.63100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -726,7 +744,7 @@
         <v>0.69799999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -743,7 +761,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -760,7 +778,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -777,7 +795,7 @@
         <v>0.80700000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -794,7 +812,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -811,7 +829,7 @@
         <v>0.86799999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -828,7 +846,7 @@
         <v>0.89400000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -845,7 +863,7 @@
         <v>0.90700000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -862,7 +880,7 @@
         <v>0.93200000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -879,7 +897,7 @@
         <v>0.93200000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -896,7 +914,7 @@
         <v>0.90900000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -913,7 +931,7 @@
         <v>0.89200000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -930,7 +948,7 @@
         <v>0.86799999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -947,7 +965,7 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -964,7 +982,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -981,7 +999,7 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -998,7 +1016,7 @@
         <v>0.78200000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1015,7 +1033,7 @@
         <v>0.752</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1032,7 +1050,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1049,7 +1067,7 @@
         <v>0.66300000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1066,7 +1084,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1083,7 +1101,7 @@
         <v>0.55300000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1100,7 +1118,7 @@
         <v>0.505</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1117,7 +1135,7 @@
         <v>0.503</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1134,7 +1152,7 @@
         <v>0.497</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1151,7 +1169,7 @@
         <v>0.49299999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1168,7 +1186,7 @@
         <v>0.498</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1185,7 +1203,7 @@
         <v>0.499</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -1202,7 +1220,7 @@
         <v>0.47199999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1219,7 +1237,7 @@
         <v>0.47199999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1235,6 +1253,172 @@
       <c r="E38" s="3">
         <v>0.47699999999999998</v>
       </c>
+    </row>
+    <row r="39" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="8"/>
+    </row>
+    <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9">
+        <v>0.93402777777777779</v>
+      </c>
+      <c r="C40" s="8"/>
+    </row>
+    <row r="41" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="9">
+        <v>0.95138888888888884</v>
+      </c>
+      <c r="C41" s="8"/>
+    </row>
+    <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="9">
+        <v>0.96875</v>
+      </c>
+      <c r="C42" s="8"/>
+    </row>
+    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="8"/>
+      <c r="B43" s="11">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="C43" s="8"/>
+    </row>
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" s="11">
+        <v>0</v>
+      </c>
+      <c r="C44" s="8"/>
+    </row>
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="8"/>
+      <c r="B45" s="11">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="C45" s="8"/>
+    </row>
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8"/>
+      <c r="B46" s="9">
+        <v>3.125E-2</v>
+      </c>
+      <c r="C46" s="8"/>
+    </row>
+    <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="8"/>
+      <c r="B47" s="9">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="C47" s="8"/>
+    </row>
+    <row r="48" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8"/>
+      <c r="B48" s="9">
+        <v>6.5972222222222224E-2</v>
+      </c>
+      <c r="C48" s="8"/>
+    </row>
+    <row r="49" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8"/>
+      <c r="B49" s="10">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C49" s="8"/>
+    </row>
+    <row r="50" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
+      <c r="B50" s="9">
+        <v>0.10069444444444445</v>
+      </c>
+      <c r="C50" s="8"/>
+    </row>
+    <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="8"/>
+      <c r="B51" s="9">
+        <v>0.11805555555555555</v>
+      </c>
+      <c r="C51" s="8"/>
+    </row>
+    <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8"/>
+      <c r="B52" s="9">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="C52" s="8"/>
+    </row>
+    <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="8"/>
+      <c r="B53" s="9">
+        <v>0.15277777777777779</v>
+      </c>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8"/>
+      <c r="B54" s="9">
+        <v>0.1701388888888889</v>
+      </c>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="55" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="8"/>
+      <c r="B55" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="C55" s="8"/>
+    </row>
+    <row r="56" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8"/>
+      <c r="B56" s="10">
+        <v>0.2048611111111111</v>
+      </c>
+      <c r="C56" s="8"/>
+    </row>
+    <row r="57" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="8"/>
+      <c r="B57" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="C57" s="8"/>
+    </row>
+    <row r="58" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="8"/>
+      <c r="B58" s="9">
+        <v>0.23958333333333334</v>
+      </c>
+      <c r="C58" s="8"/>
+    </row>
+    <row r="59" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="8"/>
+      <c r="B59" s="9">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="C59" s="8"/>
+    </row>
+    <row r="60" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="8"/>
+      <c r="B60" s="9">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="C60" s="8"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="8"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="8"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="8"/>
+      <c r="C62" s="8"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
